--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8242,0.0597,0.0342,0.0468</t>
-  </si>
-  <si>
-    <t>0.0033,0.0024,0.0009,0.9978</t>
-  </si>
-  <si>
-    <t>0.2065,0.0020,0.0016,0.9196</t>
-  </si>
-  <si>
-    <t>0.0181,0.0043,0.0026,0.9910</t>
-  </si>
-  <si>
-    <t>0.9914,0.0044,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9956,0.0011,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9909,0.0020,0.0005,0.0027</t>
-  </si>
-  <si>
-    <t>0.9959,0.0012,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9913,0.0089,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9764,0.0154,0.0003,0.0030</t>
-  </si>
-  <si>
-    <t>0.9937,0.0005,0.0001,0.0028</t>
-  </si>
-  <si>
-    <t>0.9966,0.0004,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.7208,0.0218,0.3199,0.0110</t>
-  </si>
-  <si>
-    <t>0.1663,0.0146,0.9017,0.0004</t>
-  </si>
-  <si>
-    <t>0.4129,0.0409,0.6783,0.0019</t>
-  </si>
-  <si>
-    <t>0.1317,0.0128,0.8313,0.0526</t>
-  </si>
-  <si>
-    <t>0.6137,0.0561,0.3874,0.0384</t>
-  </si>
-  <si>
-    <t>0.0050,0.9898,0.0047,0.0005</t>
-  </si>
-  <si>
-    <t>0.0184,0.9765,0.0138,0.0010</t>
-  </si>
-  <si>
-    <t>0.1702,0.8471,0.0030,0.0086</t>
-  </si>
-  <si>
-    <t>0.0370,0.9651,0.0013,0.0015</t>
-  </si>
-  <si>
-    <t>0.0020,0.9944,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.5648,0.0045,0.3977,0.0271</t>
-  </si>
-  <si>
-    <t>0.2492,0.2058,0.6272,0.0394</t>
-  </si>
-  <si>
-    <t>0.1138,0.0068,0.9332,0.0005</t>
-  </si>
-  <si>
-    <t>0.0898,0.2578,0.6814,0.0164</t>
-  </si>
-  <si>
-    <t>0.0417,0.0175,0.9351,0.0100</t>
-  </si>
-  <si>
-    <t>0.2119,0.0101,0.8044,0.0283</t>
-  </si>
-  <si>
-    <t>0.0067,0.0107,0.9605,0.0310</t>
-  </si>
-  <si>
-    <t>0.7671,0.3432,0.0068,0.0008</t>
-  </si>
-  <si>
-    <t>0.2839,0.4357,0.3804,0.0115</t>
-  </si>
-  <si>
-    <t>0.0027,0.0109,0.9924,0.0022</t>
-  </si>
-  <si>
-    <t>0.0065,0.9569,0.1017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9066,0.0261,0.0319,0.0188</t>
-  </si>
-  <si>
-    <t>0.6198,0.0561,0.4084,0.0022</t>
-  </si>
-  <si>
-    <t>0.5657,0.5825,0.0113,0.0020</t>
-  </si>
-  <si>
-    <t>0.1053,0.8309,0.1473,0.0269</t>
-  </si>
-  <si>
-    <t>0.0640,0.6497,0.1408,0.0556</t>
-  </si>
-  <si>
-    <t>0.0367,0.3849,0.8136,0.0717</t>
-  </si>
-  <si>
-    <t>0.0262,0.3367,0.8923,0.0298</t>
-  </si>
-  <si>
-    <t>0.1844,0.0014,0.7775,0.0294</t>
-  </si>
-  <si>
-    <t>0.0343,0.0341,0.9433,0.0063</t>
-  </si>
-  <si>
-    <t>0.0105,0.9139,0.0655,0.0042</t>
-  </si>
-  <si>
-    <t>0.0187,0.0928,0.9010,0.0351</t>
-  </si>
-  <si>
-    <t>0.0619,0.4021,0.0358,0.7894</t>
-  </si>
-  <si>
-    <t>0.0072,0.9566,0.0088,0.0404</t>
-  </si>
-  <si>
-    <t>0.0040,0.9559,0.3108,0.0014</t>
-  </si>
-  <si>
-    <t>0.0306,0.9345,0.0513,0.0060</t>
-  </si>
-  <si>
-    <t>0.0015,0.0438,0.9664,0.0377</t>
-  </si>
-  <si>
-    <t>0.0010,0.1999,0.9860,0.0020</t>
-  </si>
-  <si>
-    <t>0.0794,0.0423,0.8778,0.0086</t>
-  </si>
-  <si>
-    <t>0.0591,0.0033,0.9624,0.0005</t>
-  </si>
-  <si>
-    <t>0.0036,0.0529,0.9494,0.0150</t>
-  </si>
-  <si>
-    <t>0.0234,0.0443,0.9574,0.0072</t>
-  </si>
-  <si>
-    <t>0.9461,0.0557,0.0024,0.0051</t>
-  </si>
-  <si>
-    <t>0.9342,0.0194,0.0224,0.0097</t>
-  </si>
-  <si>
-    <t>0.9592,0.0203,0.0031,0.0088</t>
-  </si>
-  <si>
-    <t>0.0012,0.0046,0.9879,0.0372</t>
-  </si>
-  <si>
-    <t>0.9789,0.0041,0.0076,0.0035</t>
-  </si>
-  <si>
-    <t>0.9905,0.0024,0.0002,0.0024</t>
-  </si>
-  <si>
-    <t>0.8408,0.1842,0.0277,0.0038</t>
-  </si>
-  <si>
-    <t>0.0017,0.8773,0.8474,0.0024</t>
-  </si>
-  <si>
-    <t>0.0045,0.1532,0.9642,0.0055</t>
-  </si>
-  <si>
-    <t>0.0073,0.0565,0.9549,0.0209</t>
-  </si>
-  <si>
-    <t>0.0002,0.9558,0.9770,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.0042,0.9950,0.0007</t>
-  </si>
-  <si>
-    <t>0.0050,0.9795,0.0230,0.0008</t>
-  </si>
-  <si>
-    <t>0.0034,0.9917,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.7835,0.0287,0.2517,0.0065</t>
-  </si>
-  <si>
-    <t>0.7280,0.2202,0.0128,0.0418</t>
-  </si>
-  <si>
-    <t>0.0097,0.0330,0.9692,0.0031</t>
-  </si>
-  <si>
-    <t>0.0008,0.7426,0.9858,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9669,0.8303,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9774,0.6148,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.9435,0.8662,0.0001</t>
-  </si>
-  <si>
-    <t>0.0145,0.0065,0.0476,0.9746</t>
-  </si>
-  <si>
-    <t>0.0011,0.0095,0.0004,0.9986</t>
-  </si>
-  <si>
-    <t>0.0028,0.0006,0.0001,0.9989</t>
-  </si>
-  <si>
-    <t>0.0074,0.0009,0.0014,0.9960</t>
-  </si>
-  <si>
-    <t>0.0070,0.0027,0.0035,0.9945</t>
-  </si>
-  <si>
-    <t>0.0005,0.0018,0.0006,0.9993</t>
-  </si>
-  <si>
-    <t>0.0008,0.9348,0.9106,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.8063,0.9526,0.0004</t>
-  </si>
-  <si>
-    <t>0.0065,0.4522,0.9321,0.0035</t>
-  </si>
-  <si>
-    <t>0.0085,0.2385,0.9641,0.0010</t>
-  </si>
-  <si>
-    <t>0.0005,0.9809,0.7664,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.8760,0.9027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9831,0.0114,0.0006,0.0017</t>
-  </si>
-  <si>
-    <t>0.9347,0.0797,0.0043,0.0027</t>
-  </si>
-  <si>
-    <t>0.9832,0.0101,0.0010,0.0021</t>
-  </si>
-  <si>
-    <t>0.9861,0.0032,0.0003,0.0048</t>
-  </si>
-  <si>
-    <t>0.9680,0.0285,0.0005,0.0031</t>
-  </si>
-  <si>
-    <t>0.9889,0.0045,0.0002,0.0021</t>
-  </si>
-  <si>
-    <t>0.9288,0.0895,0.0047,0.0023</t>
-  </si>
-  <si>
-    <t>0.9742,0.0183,0.0045,0.0016</t>
-  </si>
-  <si>
-    <t>0.9957,0.0011,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9886,0.0030,0.0013,0.0027</t>
-  </si>
-  <si>
-    <t>0.9932,0.0004,0.0000,0.0042</t>
-  </si>
-  <si>
-    <t>0.9964,0.0007,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9894,0.0014,0.0003,0.0045</t>
-  </si>
-  <si>
-    <t>0.9961,0.0012,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9952,0.0005,0.0000,0.0018</t>
-  </si>
-  <si>
-    <t>0.9938,0.0014,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.0488,0.0050,0.9630,0.0029</t>
-  </si>
-  <si>
-    <t>0.4929,0.0232,0.6188,0.0032</t>
-  </si>
-  <si>
-    <t>0.7073,0.0099,0.2451,0.0337</t>
-  </si>
-  <si>
-    <t>0.1296,0.0078,0.9130,0.0026</t>
-  </si>
-  <si>
-    <t>0.0072,0.9824,0.0027,0.0006</t>
-  </si>
-  <si>
-    <t>0.0499,0.9468,0.0042,0.0020</t>
-  </si>
-  <si>
-    <t>0.2788,0.8051,0.0021,0.0019</t>
-  </si>
-  <si>
-    <t>0.3859,0.7270,0.0063,0.0029</t>
-  </si>
-  <si>
-    <t>0.0506,0.9327,0.0154,0.0058</t>
-  </si>
-  <si>
-    <t>0.0020,0.9951,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.4674,0.6312,0.0116,0.0030</t>
-  </si>
-  <si>
-    <t>0.5941,0.0768,0.3972,0.0152</t>
-  </si>
-  <si>
-    <t>0.2260,0.0264,0.7839,0.0204</t>
-  </si>
-  <si>
-    <t>0.6233,0.1266,0.2065,0.0205</t>
-  </si>
-  <si>
-    <t>0.4878,0.0184,0.5463,0.0268</t>
-  </si>
-  <si>
-    <t>0.0810,0.2885,0.0596,0.8642</t>
-  </si>
-  <si>
-    <t>0.0088,0.9811,0.0078,0.0011</t>
-  </si>
-  <si>
-    <t>0.0136,0.9585,0.0139,0.0082</t>
-  </si>
-  <si>
-    <t>0.1497,0.7459,0.0183,0.1228</t>
-  </si>
-  <si>
-    <t>0.0044,0.8538,0.8776,0.0025</t>
-  </si>
-  <si>
-    <t>0.0241,0.9589,0.0482,0.0028</t>
-  </si>
-  <si>
-    <t>0.5010,0.5219,0.0534,0.0026</t>
-  </si>
-  <si>
-    <t>0.4798,0.5813,0.0228,0.0003</t>
-  </si>
-  <si>
-    <t>0.9712,0.0142,0.0054,0.0033</t>
-  </si>
-  <si>
-    <t>0.9903,0.0017,0.0006,0.0026</t>
-  </si>
-  <si>
-    <t>0.9891,0.0008,0.0004,0.0062</t>
-  </si>
-  <si>
-    <t>0.9556,0.0341,0.0018,0.0068</t>
-  </si>
-  <si>
-    <t>0.9880,0.0032,0.0005,0.0027</t>
-  </si>
-  <si>
-    <t>0.9441,0.0370,0.0218,0.0032</t>
-  </si>
-  <si>
-    <t>0.9880,0.0013,0.0002,0.0065</t>
-  </si>
-  <si>
-    <t>0.9939,0.0010,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.0010,0.8240,0.9741,0.0003</t>
-  </si>
-  <si>
-    <t>0.0019,0.2530,0.9783,0.0000</t>
-  </si>
-  <si>
-    <t>0.0053,0.5220,0.9601,0.0011</t>
-  </si>
-  <si>
-    <t>0.0042,0.2846,0.9669,0.0010</t>
-  </si>
-  <si>
-    <t>0.6471,0.1922,0.0526,0.0687</t>
-  </si>
-  <si>
-    <t>0.8179,0.0368,0.1370,0.0142</t>
-  </si>
-  <si>
-    <t>0.4791,0.0108,0.6901,0.0024</t>
-  </si>
-  <si>
-    <t>0.4068,0.4526,0.1961,0.0126</t>
-  </si>
-  <si>
-    <t>0.0750,0.0014,0.0014,0.9748</t>
-  </si>
-  <si>
-    <t>0.0002,0.0025,0.0003,0.9996</t>
-  </si>
-  <si>
-    <t>0.0019,0.0040,0.0002,0.9986</t>
-  </si>
-  <si>
-    <t>0.0039,0.0035,0.0069,0.9953</t>
-  </si>
-  <si>
-    <t>0.0132,0.7034,0.8530,0.0024</t>
-  </si>
-  <si>
-    <t>0.9508,0.0248,0.0074,0.0092</t>
-  </si>
-  <si>
-    <t>0.6415,0.3174,0.0953,0.0291</t>
-  </si>
-  <si>
-    <t>0.9363,0.0334,0.0008,0.0115</t>
-  </si>
-  <si>
-    <t>0.9252,0.1267,0.0032,0.0010</t>
-  </si>
-  <si>
-    <t>0.9825,0.0084,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.7704,0.0192,0.0154,0.1858</t>
-  </si>
-  <si>
-    <t>0.9834,0.0037,0.0012,0.0045</t>
-  </si>
-  <si>
-    <t>0.0004,0.0105,0.9923,0.0123</t>
-  </si>
-  <si>
-    <t>0.9175,0.0001,0.0013,0.0848</t>
-  </si>
-  <si>
-    <t>0.9736,0.0007,0.0077,0.0047</t>
-  </si>
-  <si>
-    <t>0.5131,0.5075,0.0390,0.0052</t>
-  </si>
-  <si>
-    <t>0.9100,0.0500,0.0085,0.0090</t>
-  </si>
-  <si>
-    <t>0.9215,0.0295,0.0298,0.0061</t>
-  </si>
-  <si>
-    <t>0.2444,0.6667,0.0533,0.1362</t>
-  </si>
-  <si>
-    <t>0.8914,0.0560,0.0273,0.0133</t>
-  </si>
-  <si>
-    <t>0.6638,0.3614,0.0040,0.0119</t>
-  </si>
-  <si>
-    <t>0.9773,0.0041,0.0030,0.0053</t>
-  </si>
-  <si>
-    <t>0.9885,0.0049,0.0003,0.0021</t>
-  </si>
-  <si>
-    <t>0.9908,0.0007,0.0003,0.0045</t>
-  </si>
-  <si>
-    <t>0.9889,0.0002,0.0002,0.0084</t>
-  </si>
-  <si>
-    <t>0.9825,0.0036,0.0011,0.0057</t>
-  </si>
-  <si>
-    <t>0.9756,0.0116,0.0041,0.0027</t>
-  </si>
-  <si>
-    <t>0.9904,0.0020,0.0001,0.0027</t>
-  </si>
-  <si>
-    <t>0.9917,0.0011,0.0008,0.0020</t>
-  </si>
-  <si>
-    <t>0.7334,0.3288,0.0094,0.0100</t>
-  </si>
-  <si>
-    <t>0.5913,0.5250,0.0133,0.0020</t>
-  </si>
-  <si>
-    <t>0.5334,0.6270,0.0043,0.0014</t>
-  </si>
-  <si>
-    <t>0.5845,0.1797,0.4438,0.0172</t>
-  </si>
-  <si>
-    <t>0.9546,0.0618,0.0022,0.0012</t>
-  </si>
-  <si>
-    <t>0.8865,0.1140,0.0147,0.0077</t>
-  </si>
-  <si>
-    <t>0.8847,0.1859,0.0041,0.0019</t>
-  </si>
-  <si>
-    <t>0.8751,0.1598,0.0170,0.0037</t>
-  </si>
-  <si>
-    <t>0.0010,0.0302,0.9930,0.0026</t>
-  </si>
-  <si>
-    <t>0.8763,0.1852,0.0038,0.0016</t>
-  </si>
-  <si>
-    <t>0.0411,0.0240,0.9518,0.0027</t>
-  </si>
-  <si>
-    <t>0.0035,0.1038,0.9885,0.0004</t>
-  </si>
-  <si>
-    <t>0.1781,0.0287,0.8186,0.0072</t>
-  </si>
-  <si>
-    <t>0.0077,0.2053,0.9534,0.0019</t>
-  </si>
-  <si>
-    <t>0.0016,0.0841,0.9808,0.0009</t>
-  </si>
-  <si>
-    <t>0.0022,0.0011,0.9962,0.0004</t>
-  </si>
-  <si>
-    <t>0.0213,0.0087,0.9756,0.0018</t>
-  </si>
-  <si>
-    <t>0.1512,0.0946,0.8085,0.0130</t>
-  </si>
-  <si>
-    <t>0.3167,0.1819,0.5859,0.0364</t>
-  </si>
-  <si>
-    <t>0.2231,0.0314,0.8193,0.0009</t>
-  </si>
-  <si>
-    <t>0.5723,0.0208,0.5653,0.0014</t>
-  </si>
-  <si>
-    <t>0.2379,0.3884,0.2733,0.0032</t>
-  </si>
-  <si>
-    <t>0.4078,0.0769,0.5794,0.0027</t>
-  </si>
-  <si>
-    <t>0.3553,0.3068,0.4379,0.0528</t>
-  </si>
-  <si>
-    <t>0.3472,0.2413,0.5531,0.0467</t>
-  </si>
-  <si>
-    <t>0.5936,0.5869,0.0031,0.0013</t>
-  </si>
-  <si>
-    <t>0.3033,0.7937,0.0030,0.0009</t>
-  </si>
-  <si>
-    <t>0.8687,0.1610,0.0018,0.0046</t>
-  </si>
-  <si>
-    <t>0.9473,0.0795,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.5465,0.6125,0.0033,0.0017</t>
-  </si>
-  <si>
-    <t>0.3878,0.3096,0.4207,0.0346</t>
-  </si>
-  <si>
-    <t>0.8450,0.0072,0.1852,0.0051</t>
-  </si>
-  <si>
-    <t>0.6579,0.0219,0.0249,0.2565</t>
-  </si>
-  <si>
-    <t>0.5707,0.0446,0.3895,0.0211</t>
-  </si>
-  <si>
-    <t>0.7810,0.0052,0.3144,0.0043</t>
-  </si>
-  <si>
-    <t>0.0119,0.0032,0.9702,0.0355</t>
-  </si>
-  <si>
-    <t>0.0175,0.2806,0.9265,0.0229</t>
-  </si>
-  <si>
-    <t>0.0181,0.0494,0.9679,0.0025</t>
-  </si>
-  <si>
-    <t>0.0228,0.0527,0.9643,0.0038</t>
-  </si>
-  <si>
-    <t>0.0050,0.4097,0.8647,0.0039</t>
-  </si>
-  <si>
-    <t>0.9634,0.0223,0.0025,0.0062</t>
-  </si>
-  <si>
-    <t>0.9830,0.0101,0.0016,0.0016</t>
-  </si>
-  <si>
-    <t>0.9766,0.0095,0.0006,0.0056</t>
-  </si>
-  <si>
-    <t>0.9932,0.0030,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9841,0.0099,0.0014,0.0018</t>
-  </si>
-  <si>
-    <t>0.9615,0.0308,0.0050,0.0035</t>
-  </si>
-  <si>
-    <t>0.9958,0.0003,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9805,0.0083,0.0010,0.0041</t>
-  </si>
-  <si>
-    <t>0.4017,0.0742,0.6156,0.0426</t>
-  </si>
-  <si>
-    <t>0.0831,0.5170,0.6117,0.0042</t>
-  </si>
-  <si>
-    <t>0.8303,0.0599,0.0207,0.0763</t>
-  </si>
-  <si>
-    <t>0.0043,0.0149,0.9927,0.0003</t>
-  </si>
-  <si>
-    <t>0.0049,0.0270,0.9833,0.0029</t>
-  </si>
-  <si>
-    <t>0.0298,0.0720,0.9387,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0071,0.9957,0.0017</t>
-  </si>
-  <si>
-    <t>0.0962,0.0582,0.8632,0.0054</t>
-  </si>
-  <si>
-    <t>0.0046,0.0157,0.9947,0.0000</t>
-  </si>
-  <si>
-    <t>0.0567,0.1015,0.8759,0.0058</t>
-  </si>
-  <si>
-    <t>0.0481,0.0520,0.9387,0.0006</t>
-  </si>
-  <si>
-    <t>0.6921,0.0143,0.3074,0.0246</t>
-  </si>
-  <si>
-    <t>0.7662,0.0049,0.3412,0.0029</t>
-  </si>
-  <si>
-    <t>0.8422,0.0075,0.0958,0.0261</t>
-  </si>
-  <si>
-    <t>0.9834,0.0091,0.0002,0.0025</t>
-  </si>
-  <si>
-    <t>0.9757,0.0280,0.0015,0.0012</t>
-  </si>
-  <si>
-    <t>0.9936,0.0017,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.9718,0.0222,0.0007,0.0028</t>
-  </si>
-  <si>
-    <t>0.9687,0.0078,0.0001,0.0077</t>
-  </si>
-  <si>
-    <t>0.9813,0.0261,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9783,0.0159,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9612,0.0241,0.0010,0.0051</t>
-  </si>
-  <si>
-    <t>0.0103,0.0130,0.9819,0.0004</t>
-  </si>
-  <si>
-    <t>0.0030,0.0231,0.9913,0.0011</t>
-  </si>
-  <si>
-    <t>0.0164,0.2038,0.9104,0.0004</t>
-  </si>
-  <si>
-    <t>0.0151,0.1072,0.9454,0.0005</t>
-  </si>
-  <si>
-    <t>0.0110,0.0099,0.9798,0.0046</t>
-  </si>
-  <si>
-    <t>0.0469,0.0178,0.8178,0.2318</t>
-  </si>
-  <si>
-    <t>0.0593,0.0062,0.9338,0.0199</t>
-  </si>
-  <si>
-    <t>0.1574,0.0681,0.8052,0.0303</t>
-  </si>
-  <si>
-    <t>0.6229,0.0031,0.0203,0.4182</t>
-  </si>
-  <si>
-    <t>0.0079,0.2975,0.0048,0.9707</t>
-  </si>
-  <si>
-    <t>0.0103,0.0011,0.0019,0.9941</t>
-  </si>
-  <si>
-    <t>0.0024,0.0003,0.0006,0.9985</t>
-  </si>
-  <si>
-    <t>0.0023,0.0037,0.0003,0.9983</t>
-  </si>
-  <si>
-    <t>0.8819,0.0107,0.0138,0.0691</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.8785,0.0106,0.0667,0.0257</t>
+  </si>
+  <si>
+    <t>0.0058,0.0005,0.0012,0.9970</t>
+  </si>
+  <si>
+    <t>0.2921,0.0085,0.0010,0.8491</t>
+  </si>
+  <si>
+    <t>0.0277,0.0103,0.0048,0.9838</t>
+  </si>
+  <si>
+    <t>0.9904,0.0049,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9899,0.0039,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9727,0.0157,0.0036,0.0043</t>
+  </si>
+  <si>
+    <t>0.9935,0.0025,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9927,0.0036,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9611,0.0470,0.0017,0.0016</t>
+  </si>
+  <si>
+    <t>0.9963,0.0016,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9947,0.0005,0.0002,0.0021</t>
+  </si>
+  <si>
+    <t>0.8242,0.0149,0.1332,0.0154</t>
+  </si>
+  <si>
+    <t>0.3113,0.0174,0.7894,0.0028</t>
+  </si>
+  <si>
+    <t>0.2619,0.0153,0.8554,0.0008</t>
+  </si>
+  <si>
+    <t>0.0776,0.0726,0.8378,0.0079</t>
+  </si>
+  <si>
+    <t>0.7757,0.0499,0.1558,0.0179</t>
+  </si>
+  <si>
+    <t>0.0077,0.9855,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.0381,0.9482,0.0250,0.0017</t>
+  </si>
+  <si>
+    <t>0.6213,0.5176,0.0057,0.0025</t>
+  </si>
+  <si>
+    <t>0.0210,0.9765,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.0045,0.9885,0.0204,0.0003</t>
+  </si>
+  <si>
+    <t>0.6667,0.0178,0.3813,0.0195</t>
+  </si>
+  <si>
+    <t>0.2364,0.1547,0.5667,0.1865</t>
+  </si>
+  <si>
+    <t>0.0593,0.0098,0.9501,0.0016</t>
+  </si>
+  <si>
+    <t>0.1442,0.0620,0.7966,0.0134</t>
+  </si>
+  <si>
+    <t>0.3118,0.0055,0.7806,0.0046</t>
+  </si>
+  <si>
+    <t>0.2834,0.0033,0.8437,0.0016</t>
+  </si>
+  <si>
+    <t>0.0017,0.0066,0.9895,0.0022</t>
+  </si>
+  <si>
+    <t>0.5024,0.5365,0.0203,0.0018</t>
+  </si>
+  <si>
+    <t>0.2730,0.0593,0.7743,0.0020</t>
+  </si>
+  <si>
+    <t>0.0017,0.0085,0.9877,0.0094</t>
+  </si>
+  <si>
+    <t>0.0254,0.9329,0.0413,0.0017</t>
+  </si>
+  <si>
+    <t>0.8500,0.1124,0.0218,0.0181</t>
+  </si>
+  <si>
+    <t>0.4054,0.0702,0.5737,0.0167</t>
+  </si>
+  <si>
+    <t>0.6031,0.4819,0.0198,0.0020</t>
+  </si>
+  <si>
+    <t>0.0665,0.8004,0.5552,0.0171</t>
+  </si>
+  <si>
+    <t>0.0361,0.8632,0.0495,0.0291</t>
+  </si>
+  <si>
+    <t>0.2050,0.0171,0.8536,0.0075</t>
+  </si>
+  <si>
+    <t>0.1661,0.0577,0.7402,0.1181</t>
+  </si>
+  <si>
+    <t>0.1825,0.0054,0.8396,0.0205</t>
+  </si>
+  <si>
+    <t>0.0094,0.1363,0.9537,0.0025</t>
+  </si>
+  <si>
+    <t>0.0019,0.9891,0.0031,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0116,0.9862,0.0105</t>
+  </si>
+  <si>
+    <t>0.0336,0.7939,0.0136,0.3393</t>
+  </si>
+  <si>
+    <t>0.0223,0.9179,0.0278,0.0454</t>
+  </si>
+  <si>
+    <t>0.0035,0.9745,0.0844,0.0006</t>
+  </si>
+  <si>
+    <t>0.0031,0.9788,0.2008,0.0011</t>
+  </si>
+  <si>
+    <t>0.0055,0.3460,0.9683,0.0039</t>
+  </si>
+  <si>
+    <t>0.0018,0.2066,0.9885,0.0004</t>
+  </si>
+  <si>
+    <t>0.0095,0.0171,0.9731,0.0040</t>
+  </si>
+  <si>
+    <t>0.0635,0.0007,0.9707,0.0006</t>
+  </si>
+  <si>
+    <t>0.0038,0.0036,0.9913,0.0040</t>
+  </si>
+  <si>
+    <t>0.0162,0.0795,0.9494,0.0006</t>
+  </si>
+  <si>
+    <t>0.9299,0.1102,0.0034,0.0017</t>
+  </si>
+  <si>
+    <t>0.9692,0.0153,0.0076,0.0026</t>
+  </si>
+  <si>
+    <t>0.9739,0.0096,0.0045,0.0042</t>
+  </si>
+  <si>
+    <t>0.0048,0.0239,0.9830,0.0062</t>
+  </si>
+  <si>
+    <t>0.9734,0.0202,0.0025,0.0020</t>
+  </si>
+  <si>
+    <t>0.9815,0.0128,0.0009,0.0020</t>
+  </si>
+  <si>
+    <t>0.9751,0.0293,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.0016,0.8780,0.9039,0.0014</t>
+  </si>
+  <si>
+    <t>0.0081,0.2069,0.9779,0.0012</t>
+  </si>
+  <si>
+    <t>0.0023,0.0065,0.9834,0.0166</t>
+  </si>
+  <si>
+    <t>0.0008,0.8235,0.9801,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0024,0.9948,0.0018</t>
+  </si>
+  <si>
+    <t>0.0494,0.9212,0.0218,0.0016</t>
+  </si>
+  <si>
+    <t>0.0025,0.9933,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.6923,0.0474,0.3674,0.0140</t>
+  </si>
+  <si>
+    <t>0.0881,0.6545,0.5376,0.0048</t>
+  </si>
+  <si>
+    <t>0.0060,0.2241,0.8979,0.0065</t>
+  </si>
+  <si>
+    <t>0.0002,0.9665,0.9670,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.8438,0.9550,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9935,0.2082,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.8567,0.9481,0.0001</t>
+  </si>
+  <si>
+    <t>0.0281,0.0017,0.0376,0.9606</t>
+  </si>
+  <si>
+    <t>0.0016,0.0188,0.0010,0.9977</t>
+  </si>
+  <si>
+    <t>0.0014,0.0084,0.0003,0.9985</t>
+  </si>
+  <si>
+    <t>0.0051,0.0391,0.0015,0.9933</t>
+  </si>
+  <si>
+    <t>0.0114,0.0014,0.0342,0.9827</t>
+  </si>
+  <si>
+    <t>0.0058,0.0057,0.0007,0.9964</t>
+  </si>
+  <si>
+    <t>0.0003,0.9862,0.6323,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.4492,0.9736,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.5569,0.9182,0.0008</t>
+  </si>
+  <si>
+    <t>0.0068,0.2050,0.9712,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.9834,0.9848,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.8955,0.8539,0.0002</t>
+  </si>
+  <si>
+    <t>0.9828,0.0143,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.8370,0.1338,0.0010,0.0111</t>
+  </si>
+  <si>
+    <t>0.9641,0.0235,0.0067,0.0046</t>
+  </si>
+  <si>
+    <t>0.9638,0.0288,0.0006,0.0032</t>
+  </si>
+  <si>
+    <t>0.9728,0.0186,0.0010,0.0033</t>
+  </si>
+  <si>
+    <t>0.9957,0.0015,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9866,0.0058,0.0025,0.0013</t>
+  </si>
+  <si>
+    <t>0.9746,0.0287,0.0025,0.0006</t>
+  </si>
+  <si>
+    <t>0.9960,0.0003,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.9856,0.0056,0.0007,0.0029</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9977,0.0005,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9956,0.0004,0.0000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9963,0.0008,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9956,0.0007,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9850,0.0048,0.0019,0.0038</t>
+  </si>
+  <si>
+    <t>0.0135,0.0038,0.9735,0.0188</t>
+  </si>
+  <si>
+    <t>0.0934,0.0664,0.8780,0.0016</t>
+  </si>
+  <si>
+    <t>0.7415,0.0020,0.4402,0.0020</t>
+  </si>
+  <si>
+    <t>0.0228,0.0019,0.9558,0.0305</t>
+  </si>
+  <si>
+    <t>0.1188,0.9109,0.0082,0.0012</t>
+  </si>
+  <si>
+    <t>0.0160,0.9780,0.0023,0.0007</t>
+  </si>
+  <si>
+    <t>0.0188,0.9614,0.0017,0.0044</t>
+  </si>
+  <si>
+    <t>0.1213,0.9180,0.0025,0.0011</t>
+  </si>
+  <si>
+    <t>0.0050,0.9885,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.0023,0.9927,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.4855,0.6373,0.0038,0.0021</t>
+  </si>
+  <si>
+    <t>0.4447,0.3562,0.1358,0.1057</t>
+  </si>
+  <si>
+    <t>0.1969,0.0138,0.8116,0.0373</t>
+  </si>
+  <si>
+    <t>0.6411,0.0481,0.3034,0.0301</t>
+  </si>
+  <si>
+    <t>0.7459,0.0188,0.2489,0.0139</t>
+  </si>
+  <si>
+    <t>0.0952,0.7231,0.0368,0.4714</t>
+  </si>
+  <si>
+    <t>0.0055,0.9823,0.0043,0.0019</t>
+  </si>
+  <si>
+    <t>0.0387,0.9251,0.0687,0.0080</t>
+  </si>
+  <si>
+    <t>0.0339,0.7957,0.0289,0.2758</t>
+  </si>
+  <si>
+    <t>0.0007,0.7109,0.9812,0.0004</t>
+  </si>
+  <si>
+    <t>0.0381,0.9418,0.0648,0.0016</t>
+  </si>
+  <si>
+    <t>0.6069,0.3752,0.0718,0.0028</t>
+  </si>
+  <si>
+    <t>0.7290,0.3646,0.0190,0.0025</t>
+  </si>
+  <si>
+    <t>0.9531,0.0556,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9619,0.0150,0.0018,0.0107</t>
+  </si>
+  <si>
+    <t>0.9906,0.0004,0.0001,0.0078</t>
+  </si>
+  <si>
+    <t>0.9803,0.0033,0.0035,0.0051</t>
+  </si>
+  <si>
+    <t>0.9914,0.0020,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.8755,0.0512,0.0772,0.0135</t>
+  </si>
+  <si>
+    <t>0.9841,0.0024,0.0019,0.0043</t>
+  </si>
+  <si>
+    <t>0.9903,0.0009,0.0005,0.0046</t>
+  </si>
+  <si>
+    <t>0.0005,0.9157,0.9700,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.6755,0.9440,0.0001</t>
+  </si>
+  <si>
+    <t>0.0091,0.2425,0.9479,0.0015</t>
+  </si>
+  <si>
+    <t>0.0305,0.2076,0.9106,0.0010</t>
+  </si>
+  <si>
+    <t>0.7950,0.0372,0.1272,0.0162</t>
+  </si>
+  <si>
+    <t>0.5670,0.1155,0.3584,0.0069</t>
+  </si>
+  <si>
+    <t>0.4027,0.0071,0.7041,0.0101</t>
+  </si>
+  <si>
+    <t>0.7844,0.1116,0.0475,0.0089</t>
+  </si>
+  <si>
+    <t>0.0943,0.0008,0.0007,0.9741</t>
+  </si>
+  <si>
+    <t>0.0003,0.0021,0.0004,0.9995</t>
+  </si>
+  <si>
+    <t>0.0071,0.0017,0.0010,0.9965</t>
+  </si>
+  <si>
+    <t>0.0175,0.0006,0.0007,0.9949</t>
+  </si>
+  <si>
+    <t>0.0004,0.9916,0.0568,0.0001</t>
+  </si>
+  <si>
+    <t>0.9772,0.0097,0.0005,0.0043</t>
+  </si>
+  <si>
+    <t>0.2500,0.7420,0.0283,0.0261</t>
+  </si>
+  <si>
+    <t>0.9557,0.0235,0.0049,0.0058</t>
+  </si>
+  <si>
+    <t>0.5379,0.5765,0.0137,0.0058</t>
+  </si>
+  <si>
+    <t>0.9607,0.0050,0.0058,0.0164</t>
+  </si>
+  <si>
+    <t>0.5809,0.0094,0.0390,0.4315</t>
+  </si>
+  <si>
+    <t>0.9796,0.0035,0.0102,0.0018</t>
+  </si>
+  <si>
+    <t>0.0015,0.0069,0.9852,0.0326</t>
+  </si>
+  <si>
+    <t>0.9549,0.0019,0.0070,0.0224</t>
+  </si>
+  <si>
+    <t>0.9798,0.0006,0.0009,0.0121</t>
+  </si>
+  <si>
+    <t>0.0357,0.9476,0.0108,0.0031</t>
+  </si>
+  <si>
+    <t>0.9062,0.0634,0.0207,0.0031</t>
+  </si>
+  <si>
+    <t>0.8806,0.1522,0.0064,0.0023</t>
+  </si>
+  <si>
+    <t>0.1427,0.8324,0.0283,0.0145</t>
+  </si>
+  <si>
+    <t>0.6158,0.4385,0.0113,0.0085</t>
+  </si>
+  <si>
+    <t>0.6119,0.4281,0.0351,0.0239</t>
+  </si>
+  <si>
+    <t>0.9781,0.0093,0.0031,0.0034</t>
+  </si>
+  <si>
+    <t>0.9924,0.0016,0.0002,0.0021</t>
+  </si>
+  <si>
+    <t>0.9883,0.0045,0.0013,0.0018</t>
+  </si>
+  <si>
+    <t>0.9816,0.0035,0.0016,0.0065</t>
+  </si>
+  <si>
+    <t>0.9766,0.0138,0.0012,0.0035</t>
+  </si>
+  <si>
+    <t>0.9729,0.0307,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9893,0.0019,0.0014,0.0022</t>
+  </si>
+  <si>
+    <t>0.9853,0.0009,0.0002,0.0097</t>
+  </si>
+  <si>
+    <t>0.3685,0.7133,0.0246,0.0049</t>
+  </si>
+  <si>
+    <t>0.4023,0.6721,0.0180,0.0016</t>
+  </si>
+  <si>
+    <t>0.7579,0.2939,0.0281,0.0034</t>
+  </si>
+  <si>
+    <t>0.0723,0.7257,0.6494,0.0071</t>
+  </si>
+  <si>
+    <t>0.9721,0.0262,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.8044,0.1488,0.0241,0.0403</t>
+  </si>
+  <si>
+    <t>0.9633,0.0481,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9134,0.1228,0.0032,0.0013</t>
+  </si>
+  <si>
+    <t>0.0019,0.0089,0.9919,0.0071</t>
+  </si>
+  <si>
+    <t>0.8944,0.1188,0.0083,0.0075</t>
+  </si>
+  <si>
+    <t>0.0029,0.0058,0.9919,0.0015</t>
+  </si>
+  <si>
+    <t>0.0012,0.1266,0.9844,0.0030</t>
+  </si>
+  <si>
+    <t>0.0130,0.0321,0.9732,0.0022</t>
+  </si>
+  <si>
+    <t>0.0080,0.0207,0.9841,0.0016</t>
+  </si>
+  <si>
+    <t>0.0088,0.0297,0.9835,0.0006</t>
+  </si>
+  <si>
+    <t>0.0082,0.0170,0.9754,0.0018</t>
+  </si>
+  <si>
+    <t>0.0038,0.0039,0.9919,0.0005</t>
+  </si>
+  <si>
+    <t>0.2521,0.1659,0.6493,0.0110</t>
+  </si>
+  <si>
+    <t>0.1817,0.0223,0.8807,0.0020</t>
+  </si>
+  <si>
+    <t>0.3115,0.0373,0.2060,0.5950</t>
+  </si>
+  <si>
+    <t>0.6032,0.0496,0.4156,0.0041</t>
+  </si>
+  <si>
+    <t>0.1812,0.0574,0.8190,0.0043</t>
+  </si>
+  <si>
+    <t>0.3848,0.0509,0.6738,0.0076</t>
+  </si>
+  <si>
+    <t>0.7075,0.0302,0.3314,0.0139</t>
+  </si>
+  <si>
+    <t>0.5972,0.0063,0.6022,0.0024</t>
+  </si>
+  <si>
+    <t>0.6806,0.5000,0.0050,0.0007</t>
+  </si>
+  <si>
+    <t>0.3156,0.8303,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.8497,0.2114,0.0054,0.0024</t>
+  </si>
+  <si>
+    <t>0.8850,0.2065,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.8568,0.1224,0.0014,0.0079</t>
+  </si>
+  <si>
+    <t>0.6014,0.0494,0.4269,0.0019</t>
+  </si>
+  <si>
+    <t>0.8266,0.0044,0.2366,0.0036</t>
+  </si>
+  <si>
+    <t>0.8597,0.0095,0.0617,0.0227</t>
+  </si>
+  <si>
+    <t>0.5845,0.0109,0.5004,0.0133</t>
+  </si>
+  <si>
+    <t>0.7539,0.1133,0.0560,0.0376</t>
+  </si>
+  <si>
+    <t>0.0015,0.0035,0.9835,0.0527</t>
+  </si>
+  <si>
+    <t>0.0028,0.5866,0.9616,0.0010</t>
+  </si>
+  <si>
+    <t>0.0135,0.2952,0.9408,0.0023</t>
+  </si>
+  <si>
+    <t>0.1722,0.1775,0.7005,0.0277</t>
+  </si>
+  <si>
+    <t>0.0012,0.9061,0.3771,0.0019</t>
+  </si>
+  <si>
+    <t>0.9921,0.0027,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9768,0.0103,0.0063,0.0023</t>
+  </si>
+  <si>
+    <t>0.9820,0.0096,0.0014,0.0029</t>
+  </si>
+  <si>
+    <t>0.9709,0.0226,0.0010,0.0034</t>
+  </si>
+  <si>
+    <t>0.9883,0.0044,0.0008,0.0021</t>
+  </si>
+  <si>
+    <t>0.9864,0.0063,0.0013,0.0019</t>
+  </si>
+  <si>
+    <t>0.9762,0.0019,0.0011,0.0159</t>
+  </si>
+  <si>
+    <t>0.9867,0.0080,0.0012,0.0014</t>
+  </si>
+  <si>
+    <t>0.0697,0.0155,0.8922,0.0490</t>
+  </si>
+  <si>
+    <t>0.1749,0.5824,0.5229,0.0283</t>
+  </si>
+  <si>
+    <t>0.6235,0.0593,0.1797,0.1376</t>
+  </si>
+  <si>
+    <t>0.0091,0.0253,0.9825,0.0003</t>
+  </si>
+  <si>
+    <t>0.0094,0.0092,0.9773,0.0062</t>
+  </si>
+  <si>
+    <t>0.0112,0.1924,0.9398,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0036,0.9968,0.0029</t>
+  </si>
+  <si>
+    <t>0.0976,0.0158,0.9137,0.0014</t>
+  </si>
+  <si>
+    <t>0.0027,0.0074,0.9928,0.0010</t>
+  </si>
+  <si>
+    <t>0.0124,0.0484,0.9684,0.0037</t>
+  </si>
+  <si>
+    <t>0.0150,0.0380,0.9518,0.0095</t>
+  </si>
+  <si>
+    <t>0.7526,0.0028,0.1774,0.0297</t>
+  </si>
+  <si>
+    <t>0.4659,0.0215,0.6307,0.0110</t>
+  </si>
+  <si>
+    <t>0.8337,0.0062,0.1514,0.0143</t>
+  </si>
+  <si>
+    <t>0.9868,0.0028,0.0000,0.0028</t>
+  </si>
+  <si>
+    <t>0.9732,0.0230,0.0011,0.0023</t>
+  </si>
+  <si>
+    <t>0.9953,0.0022,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9398,0.0734,0.0037,0.0026</t>
+  </si>
+  <si>
+    <t>0.9893,0.0054,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9743,0.0240,0.0010,0.0017</t>
+  </si>
+  <si>
+    <t>0.9845,0.0160,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9908,0.0056,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.0274,0.1094,0.9195,0.0014</t>
+  </si>
+  <si>
+    <t>0.0034,0.0948,0.9810,0.0008</t>
+  </si>
+  <si>
+    <t>0.0036,0.5133,0.9536,0.0008</t>
+  </si>
+  <si>
+    <t>0.0495,0.0268,0.9331,0.0017</t>
+  </si>
+  <si>
+    <t>0.0148,0.0082,0.9785,0.0044</t>
+  </si>
+  <si>
+    <t>0.2521,0.0127,0.7562,0.0273</t>
+  </si>
+  <si>
+    <t>0.0355,0.0545,0.9239,0.0061</t>
+  </si>
+  <si>
+    <t>0.0595,0.0312,0.7376,0.2894</t>
+  </si>
+  <si>
+    <t>0.6804,0.0010,0.0026,0.4575</t>
+  </si>
+  <si>
+    <t>0.0146,0.3852,0.0032,0.9586</t>
+  </si>
+  <si>
+    <t>0.0114,0.0011,0.0008,0.9955</t>
+  </si>
+  <si>
+    <t>0.0035,0.0005,0.0013,0.9975</t>
+  </si>
+  <si>
+    <t>0.0012,0.0013,0.0006,0.9989</t>
+  </si>
+  <si>
+    <t>0.6544,0.0124,0.1475,0.1620</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1993,7 @@
         <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2228,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2466,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2984,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3141,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3866,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4373,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4667,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4860,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5045,7 @@
         <v>263</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5364,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
